--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.45524411172184</v>
+      </c>
+      <c r="C2">
         <v>25.91339816449872</v>
-      </c>
-      <c r="C2">
-        <v>28.45524411172184</v>
       </c>
       <c r="D2">
         <v>3.859007582301564</v>
       </c>
       <c r="E2">
-        <v>16.78669824544444</v>
+        <v>18.4333059435771</v>
       </c>
       <c r="F2">
         <v>64.77999581097846</v>
       </c>
       <c r="G2">
-        <v>18.4333059435771</v>
+        <v>16.78669824544444</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>20.73921971252567</v>
+      </c>
+      <c r="C3">
         <v>40.6570841889117</v>
-      </c>
-      <c r="C3">
-        <v>20.73921971252567</v>
       </c>
       <c r="D3">
         <v>2.45959595959596</v>
       </c>
       <c r="E3">
-        <v>25.19083969465649</v>
+        <v>12.8498727735369</v>
       </c>
       <c r="F3">
         <v>61.95928753180662</v>
       </c>
       <c r="G3">
-        <v>12.8498727735369</v>
+        <v>25.19083969465649</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.96274868646319</v>
+      </c>
+      <c r="C4">
         <v>25.09593246354566</v>
-      </c>
-      <c r="C4">
-        <v>28.96274868646319</v>
       </c>
       <c r="D4">
         <v>3.984709480122324</v>
       </c>
       <c r="E4">
-        <v>16.28985285101165</v>
+        <v>18.79981606376456</v>
       </c>
       <c r="F4">
         <v>64.91033108522379</v>
       </c>
       <c r="G4">
-        <v>18.79981606376456</v>
+        <v>16.28985285101165</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.53162440791307</v>
+      </c>
+      <c r="C5">
         <v>23.73920312064642</v>
-      </c>
-      <c r="C5">
-        <v>28.53162440791307</v>
       </c>
       <c r="D5">
         <v>4.212441314553991</v>
       </c>
       <c r="E5">
-        <v>15.59011893870082</v>
+        <v>18.73741994510522</v>
       </c>
       <c r="F5">
-        <v>65.67246111619396</v>
+        <v>65.67246111619397</v>
       </c>
       <c r="G5">
-        <v>18.73741994510522</v>
+        <v>15.59011893870083</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.84801548886738</v>
+      </c>
+      <c r="C6">
         <v>20.42594385285576</v>
-      </c>
-      <c r="C6">
-        <v>28.84801548886738</v>
       </c>
       <c r="D6">
         <v>4.895734597156398</v>
       </c>
       <c r="E6">
-        <v>13.68352788586251</v>
+        <v>19.32555123216602</v>
       </c>
       <c r="F6">
         <v>66.99092088197146</v>
       </c>
       <c r="G6">
-        <v>19.32555123216602</v>
+        <v>13.68352788586251</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.47341337907376</v>
+      </c>
+      <c r="C7">
         <v>28.73070325900515</v>
-      </c>
-      <c r="C7">
-        <v>28.47341337907376</v>
       </c>
       <c r="D7">
         <v>3.480597014925373</v>
       </c>
       <c r="E7">
-        <v>18.27605019094381</v>
+        <v>18.11238406983088</v>
       </c>
       <c r="F7">
         <v>63.61156573922532</v>
       </c>
       <c r="G7">
-        <v>18.11238406983088</v>
+        <v>18.27605019094381</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>20.05988023952096</v>
+      </c>
+      <c r="C8">
         <v>9.580838323353294</v>
-      </c>
-      <c r="C8">
-        <v>20.05988023952096</v>
       </c>
       <c r="D8">
         <v>10.4375</v>
       </c>
       <c r="E8">
-        <v>7.390300230946884</v>
+        <v>15.47344110854503</v>
       </c>
       <c r="F8">
-        <v>77.13625866050809</v>
+        <v>77.13625866050808</v>
       </c>
       <c r="G8">
-        <v>15.47344110854504</v>
+        <v>7.390300230946882</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.398753894081</v>
+      </c>
+      <c r="C9">
         <v>16.1993769470405</v>
-      </c>
-      <c r="C9">
-        <v>32.398753894081</v>
       </c>
       <c r="D9">
         <v>6.173076923076923</v>
       </c>
       <c r="E9">
-        <v>10.90146750524109</v>
+        <v>21.80293501048218</v>
       </c>
       <c r="F9">
         <v>67.29559748427674</v>
       </c>
       <c r="G9">
-        <v>21.80293501048218</v>
+        <v>10.90146750524109</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.56679914399266</v>
+      </c>
+      <c r="C10">
         <v>38.73433200856007</v>
-      </c>
-      <c r="C10">
-        <v>26.56679914399266</v>
       </c>
       <c r="D10">
         <v>2.581689029202841</v>
       </c>
       <c r="E10">
-        <v>23.43258738672092</v>
+        <v>16.07175883114482</v>
       </c>
       <c r="F10">
         <v>60.49565378213428</v>
       </c>
       <c r="G10">
-        <v>16.07175883114482</v>
+        <v>23.43258738672092</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.56993222427603</v>
+      </c>
+      <c r="C11">
         <v>39.74121996303142</v>
-      </c>
-      <c r="C11">
-        <v>25.56993222427603</v>
       </c>
       <c r="D11">
         <v>2.516279069767442</v>
       </c>
       <c r="E11">
+        <v>15.46775997018263</v>
+      </c>
+      <c r="F11">
+        <v>60.49198658218413</v>
+      </c>
+      <c r="G11">
         <v>24.04025344763324</v>
-      </c>
-      <c r="F11">
-        <v>60.49198658218412</v>
-      </c>
-      <c r="G11">
-        <v>15.46775997018263</v>
       </c>
     </row>
   </sheetData>
